--- a/owlcms/src/main/resources/templates/jury/JuryExam-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/jury/JuryExam-LETTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\jury\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\jury\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60052AC-EB5D-42AA-95B2-D02565368A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30AB7CDD-D3E1-4A8F-8CB9-9ACA32DCB5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37620" yWindow="-6840" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jury" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="57">
   <si>
     <t>#</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>${t.get("Jury.incorrect.Title")}</t>
+  </si>
+  <si>
+    <t>${session.competitionTimeAsExcelDate}</t>
   </si>
 </sst>
 </file>
@@ -716,15 +719,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -769,6 +763,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -798,23 +801,7 @@
     <cellStyle name="Titre 1 1 1 1 1" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
     <cellStyle name="Titre de la feuille" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1356,26 +1343,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
       <c r="L1" s="27"/>
     </row>
     <row r="2" spans="1:12" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="57"/>
+      <c r="B2" s="54"/>
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1393,21 +1380,21 @@
       <c r="K2" s="26"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
       <c r="G3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H3" s="36" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="I3" s="28" t="s">
         <v>13</v>
@@ -1422,11 +1409,11 @@
       <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
       <c r="F4" s="22"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -1444,25 +1431,25 @@
       <c r="B6" s="4"/>
       <c r="C6" s="7"/>
       <c r="D6" s="8"/>
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="54"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="54" t="s">
+      <c r="G6" s="51"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="54"/>
-      <c r="K6" s="56"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="53"/>
     </row>
     <row r="7" spans="1:12" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="60"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="9" t="s">
         <v>17</v>
       </c>
@@ -1497,10 +1484,10 @@
       <c r="A9" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="62"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="35" t="s">
         <v>24</v>
       </c>
@@ -1531,10 +1518,10 @@
       <c r="I11" s="15"/>
     </row>
     <row r="12" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="50"/>
+      <c r="B12" s="47"/>
       <c r="C12" s="16"/>
       <c r="D12" s="17"/>
       <c r="E12" s="18"/>
@@ -1777,22 +1764,17 @@
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <conditionalFormatting sqref="B9:B10">
-    <cfRule type="expression" dxfId="5" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11:C11 J12 C12">
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+  <conditionalFormatting sqref="B11:C11 C12 J12">
+    <cfRule type="expression" dxfId="2" priority="8" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D10">
-    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9:E10">
-    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="D9:E10">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1830,10 +1812,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="57"/>
+      <c r="B2" s="54"/>
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1851,16 +1833,16 @@
       <c r="K2" s="26"/>
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
       <c r="G3" s="4" t="s">
         <v>11</v>
       </c>
@@ -1880,11 +1862,11 @@
       <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
       <c r="F4" s="22"/>
       <c r="I4" s="28" t="s">
         <v>14</v>
@@ -2002,10 +1984,10 @@
       <c r="I11" s="15"/>
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="50"/>
+      <c r="B12" s="47"/>
       <c r="C12" s="16"/>
       <c r="D12" s="17"/>
       <c r="E12" s="18"/>
@@ -2033,182 +2015,182 @@
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="20"/>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
     </row>
     <row r="15" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="20"/>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47" t="s">
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="60"/>
     </row>
     <row r="16" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="20"/>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47" t="s">
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="47"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
     </row>
     <row r="17" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="20"/>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47" t="s">
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="47"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="20"/>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47" t="s">
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
     </row>
     <row r="19" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="20"/>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47" t="s">
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="60"/>
     </row>
     <row r="20" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="20"/>
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47" t="s">
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="60"/>
     </row>
     <row r="21" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="20"/>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47" t="s">
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
     </row>
     <row r="22" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="20"/>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47" t="s">
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
     </row>
     <row r="23" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="20"/>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
     </row>
     <row r="24" spans="1:11" s="1" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="20"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
     </row>
     <row r="25" spans="1:11" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
@@ -2226,18 +2208,14 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="G18:K18"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="G23:K23"/>
-    <mergeCell ref="G24:K24"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="G15:K15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="G16:K16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="G17:K17"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="G14:K14"/>
     <mergeCell ref="B22:F22"/>
@@ -2248,14 +2226,18 @@
     <mergeCell ref="G19:K19"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="G20:K20"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="G16:K16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="G17:K17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="G24:K24"/>
+    <mergeCell ref="B24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="B7:C11 J12 C12:C13 B13 C25">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
